--- a/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 15,92</t>
+          <t>-13,16; 16,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 18,64</t>
+          <t>-21,96; 18,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 29,75</t>
+          <t>-4,05; 29,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-85,55; 383,73</t>
+          <t>-83,31; 311,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,22; 1616,52</t>
+          <t>-50,19; 1254,67</t>
         </is>
       </c>
     </row>
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 0,53</t>
+          <t>-44,65; 2,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 29,59</t>
+          <t>-14,14; 29,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 6,65</t>
+          <t>-16,43; 7,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,26</t>
+          <t>-100,0; 144,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 875,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 26,42</t>
+          <t>-16,89; 25,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 31,33</t>
+          <t>-27,56; 31,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 5,77</t>
+          <t>-46,21; 8,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,99</t>
+          <t>-100,0; 98,45</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 7,38</t>
+          <t>-16,1; 7,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 10,96</t>
+          <t>-17,55; 10,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 11,83</t>
+          <t>-31,3; 12,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 63,19</t>
+          <t>-66,35; 70,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 92,48</t>
+          <t>-60,35; 85,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,75; 83,4</t>
+          <t>-86,17; 67,1</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 16,23</t>
+          <t>-12,92; 15,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 13,35</t>
+          <t>-23,71; 13,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 26,41</t>
+          <t>-5,47; 25,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-75,38; 320,74</t>
+          <t>-67,92; 283,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,31; 104,57</t>
+          <t>-72,01; 102,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 473,99</t>
+          <t>-40,7; 426,93</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 37,03</t>
+          <t>-27,23; 31,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 9,92</t>
+          <t>-44,93; 7,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 41,34</t>
+          <t>-19,08; 43,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 364,7</t>
+          <t>-44,84; 369,24</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,76</t>
+          <t>-10,68; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 5,91</t>
+          <t>-10,77; 5,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 9,96</t>
+          <t>-10,78; 9,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-56,13; 23,9</t>
+          <t>-52,91; 25,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 41,49</t>
+          <t>-43,97; 34,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 69,24</t>
+          <t>-47,52; 61,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 16,48</t>
+          <t>-13,01; 15,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 18,46</t>
+          <t>-21,1; 19,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 29,86</t>
+          <t>-3,07; 29,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,31; 311,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 1254,67</t>
+          <t>-57,61; 1232,05</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 2,35</t>
+          <t>-44,69; 3,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 29,53</t>
+          <t>-12,43; 30,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 7,25</t>
+          <t>-17,77; 6,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 25,83</t>
+          <t>-16,75; 25,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 31,81</t>
+          <t>-26,14; 31,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 8,18</t>
+          <t>-45,09; 8,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,45</t>
+          <t>-100,0; 117,38</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 7,4</t>
+          <t>-16,51; 7,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 10,79</t>
+          <t>-17,53; 12,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 12,07</t>
+          <t>-33,65; 12,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,35; 70,8</t>
+          <t>-66,8; 69,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 85,18</t>
+          <t>-59,5; 100,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,17; 67,1</t>
+          <t>-88,41; 87,16</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 15,51</t>
+          <t>-13,01; 17,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 13,02</t>
+          <t>-23,28; 13,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 25,75</t>
+          <t>-5,26; 27,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-67,92; 283,73</t>
+          <t>-69,75; 342,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-72,01; 102,88</t>
+          <t>-70,63; 97,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,7; 426,93</t>
+          <t>-30,7; 448,51</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 31,6</t>
+          <t>-24,51; 37,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 7,68</t>
+          <t>-39,43; 10,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 43,87</t>
+          <t>-17,49; 43,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 749,22</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 369,24</t>
+          <t>-47,71; 395,53</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 3,03</t>
+          <t>-9,91; 3,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 5,31</t>
+          <t>-10,78; 5,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 9,52</t>
+          <t>-10,65; 9,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-52,91; 25,68</t>
+          <t>-51,41; 29,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 34,78</t>
+          <t>-44,72; 35,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 61,3</t>
+          <t>-49,66; 63,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,91</t>
+          <t>13,28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>166,13%</t>
+          <t>146,21%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 15,49</t>
+          <t>-13,53; 15,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 19,05</t>
+          <t>-23,08; 18,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 29,49</t>
+          <t>-6,6; 29,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,55; 383,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 1232,05</t>
+          <t>-54,87; 1717,62</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-43,27%</t>
+          <t>-38,17%</t>
         </is>
       </c>
     </row>
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 3,13</t>
+          <t>-41,78; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 30,31</t>
+          <t>-15,48; 29,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 6,62</t>
+          <t>-16,23; 6,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 83,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 875,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-19,12</t>
+          <t>-18,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-62,37%</t>
+          <t>-62,21%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 25,82</t>
+          <t>-17,15; 26,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 31,64</t>
+          <t>-25,31; 31,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 8,41</t>
+          <t>-44,75; 7,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 117,38</t>
+          <t>-100,0; 176,35</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-10,22</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,18%</t>
+          <t>-36,98%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 7,08</t>
+          <t>-16,19; 7,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 12,19</t>
+          <t>-18,3; 10,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 12,94</t>
+          <t>-31,29; 5,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 69,35</t>
+          <t>-68,21; 63,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,5; 100,6</t>
+          <t>-63,63; 92,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,41; 87,16</t>
+          <t>-75,86; 42,85</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 17,04</t>
+          <t>-14,11; 16,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 13,54</t>
+          <t>-23,32; 13,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 27,45</t>
+          <t>-5,5; 24,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 342,71</t>
+          <t>-75,38; 320,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 97,6</t>
+          <t>-70,31; 104,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 448,51</t>
+          <t>-30,41; 449,56</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,51</t>
+          <t>16,42</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 37,96</t>
+          <t>-25,5; 37,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,43; 10,26</t>
+          <t>-43,4; 9,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 43,16</t>
+          <t>-12,19; 43,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 749,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 395,53</t>
+          <t>-36,68; 459,52</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,02%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 3,43</t>
+          <t>-10,93; 2,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 5,3</t>
+          <t>-10,37; 5,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 9,87</t>
+          <t>-8,97; 7,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 29,88</t>
+          <t>-56,13; 23,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 35,23</t>
+          <t>-43,18; 41,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 63,96</t>
+          <t>-37,12; 55,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,6 +524,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,43 +542,55 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -582,6 +605,8 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -594,239 +619,173 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>146,21%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.6151656127493925</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.05841812950049263</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.02451147898331479</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.204933260873527</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.02567511863972639</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.008408036297476438</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.492375269344326</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,53; 15,92</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-23,08; 18,64</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,6; 29,33</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-85,55; 383,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-54,87; 1717,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.723401134050121</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.252473735204545</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.829620883850137</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="n">
+        <v>-0.8754895329188542</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.7562957738111629</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.964872151425972</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.587601398768066</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.776854117278732</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.672355494108453</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n">
+        <v>4.204062070470671</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>15.14136848992957</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-16,88</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,47</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-72,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>47,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-38,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-41,78; 0,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-15,48; 29,59</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-16,23; 6,77</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 83,26</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 875,79</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.410158669214694</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.02058586127339744</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.8265561708027381</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>-0.4867032674620755</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01055423133108314</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4056368269090029</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-18,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-62,21%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>-5.393494379858368</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.250683489154772</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.910408683024861</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-17,15; 26,42</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-25,31; 31,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-44,75; 7,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 176,35</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>1.578745590484509</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.101452742355147</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.707272768990597</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +793,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-4,6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-10,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-25,23%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-15,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-36,98%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.01484030910563778</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4235802253257342</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.964957432398517</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-0.009569748078940196</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.156921614271176</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.7451247889237294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-16,19; 7,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-18,3; 10,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-31,29; 5,61</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-68,21; 63,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-63,63; 92,48</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-75,86; 42,85</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-3.00472655991013</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.620101432667962</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-14.29655172378756</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>2.955607795841563</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.576373166163579</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.3506763910817262</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>1.273487413451458</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-5,28</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-21,71%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>75,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-14,11; 16,23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-23,32; 13,35</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,5; 24,84</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-75,38; 320,74</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-70,31; 104,57</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-30,41; 449,56</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.6603826151456533</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.375703187801598</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2620107084184136</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.664776736239165</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.29948921966882</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07446956796295177</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3913715594727641</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-13,58</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16,42</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-2,29%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-59,46%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,4%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.317203142177028</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.539796453847563</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.346306011854455</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-11.14985765439508</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.6864020864916722</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4993424227128799</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.8446371745278234</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-25,5; 37,03</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-43,4; 9,92</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-12,19; 43,34</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-36,68; 459,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.436490221839793</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.164546510306793</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.335322145192897</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>0.5663146518070048</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.543391949254582</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.3712194223548756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +971,275 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-3,49</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,51</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-22,14%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-12,73%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4077223860411671</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6403956287756918</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.608784689712977</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="n">
+        <v>0.1681127953396493</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1467274689039323</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.9636230345045934</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-10,93; 2,76</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-10,37; 5,91</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-8,97; 7,72</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-56,13; 23,9</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-43,18; 41,49</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-37,12; 55,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="n">
+        <v>-2.817876690694022</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.639348841986507</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.171474674176349</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.7468036735415566</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.7369419745499408</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4200547773436125</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="n">
+        <v>3.453137628019551</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.186691522315736</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.770985421327913</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>3.429533923157426</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.396323942567244</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>4.879918547651514</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-0.8941918691158875</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.173399464647271</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-1.318888682799401</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2.169209980031338</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.320845738845877</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.4004624362184189</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.4244984138655871</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.709092283942285</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-5.613776726230628</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-6.724829137891586</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-4.331924989817701</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="n">
+        <v>-0.5995347628253127</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4.169818352406911</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.730428768011429</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>8.763709663814927</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>5.717471157582152</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="n">
+        <v>4.429418384329475</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.1889973219872692</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.6862305326753846</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.1038048057458919</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.1130094476880929</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.6528858684222772</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.2157570910065035</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.03197397930434927</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.02569524409868826</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.5778033023156286</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.056486152463346</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.651196381333278</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.51565430133237</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="n">
+        <v>-0.5329166255044842</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.4231938704356947</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.4317789902970222</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.2027534654102386</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.7366537606887713</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.393933276688175</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.907151303919822</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="n">
+        <v>0.3328639287374745</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.544854173166968</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.5999026984288858</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1152,16 +1247,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
